--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122923765</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122923765</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125852607</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105908</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogsväg S Rosenhäll, Äsperöd, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>322910</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6470843</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rune Hixén, Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105915</v>
+        <v>105916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105916</v>
+        <v>105918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105922</v>
+        <v>105923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105923</v>
+        <v>105925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105927</v>
+        <v>105931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>125852607</v>
       </c>
       <c r="B3" t="n">
-        <v>105947</v>
+        <v>105956</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,119 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128390975</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Äsperöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>322703</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6470617</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna Lindstein</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Lindstein</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>128390975</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>128390975</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62068-2024 artfynd.xlsx
+++ b/artfynd/A 62068-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>128390975</v>
       </c>
       <c r="B4" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
